--- a/artfynd/A 12268-2024 artfynd.xlsx
+++ b/artfynd/A 12268-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104023107</v>
+        <v>104023138</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551271.673898346</v>
+        <v>551332</v>
       </c>
       <c r="R2" t="n">
-        <v>6996736.715350322</v>
+        <v>6996604</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104023121</v>
+        <v>104023107</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551296.6056916434</v>
+        <v>551271</v>
       </c>
       <c r="R3" t="n">
-        <v>6996709.025660204</v>
+        <v>6996737</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104023104</v>
+        <v>104023120</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551330.3261193908</v>
+        <v>551292</v>
       </c>
       <c r="R4" t="n">
-        <v>6996670.603633642</v>
+        <v>6996731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104023135</v>
+        <v>104023104</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551214.0222315388</v>
+        <v>551330</v>
       </c>
       <c r="R5" t="n">
-        <v>6996710.89131844</v>
+        <v>6996671</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104023120</v>
+        <v>104023121</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551292.626912288</v>
+        <v>551297</v>
       </c>
       <c r="R6" t="n">
-        <v>6996731.158115527</v>
+        <v>6996709</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,6 +1223,122 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104023134</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hundtjärnåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>551421</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6996485</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 12268-2024 artfynd.xlsx
+++ b/artfynd/A 12268-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023107</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023121</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023134</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023138</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,8 +1373,21 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023104</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>